--- a/r5-ELGA-MOPED-354-operations-updaten-und-erheben/ValueSet-moped-entlassungsart-valueset.xlsx
+++ b/r5-ELGA-MOPED-354-operations-updaten-und-erheben/ValueSet-moped-entlassungsart-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T15:46:55+00:00</t>
+    <t>2025-02-13T19:10:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-354-operations-updaten-und-erheben/ValueSet-moped-entlassungsart-valueset.xlsx
+++ b/r5-ELGA-MOPED-354-operations-updaten-und-erheben/ValueSet-moped-entlassungsart-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T19:10:28+00:00</t>
+    <t>2025-02-13T19:15:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-354-operations-updaten-und-erheben/ValueSet-moped-entlassungsart-valueset.xlsx
+++ b/r5-ELGA-MOPED-354-operations-updaten-und-erheben/ValueSet-moped-entlassungsart-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T19:15:24+00:00</t>
+    <t>2025-02-13T19:19:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-354-operations-updaten-und-erheben/ValueSet-moped-entlassungsart-valueset.xlsx
+++ b/r5-ELGA-MOPED-354-operations-updaten-und-erheben/ValueSet-moped-entlassungsart-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T19:19:51+00:00</t>
+    <t>2025-02-13T19:26:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-354-operations-updaten-und-erheben/ValueSet-moped-entlassungsart-valueset.xlsx
+++ b/r5-ELGA-MOPED-354-operations-updaten-und-erheben/ValueSet-moped-entlassungsart-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T19:26:41+00:00</t>
+    <t>2025-02-13T19:32:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-354-operations-updaten-und-erheben/ValueSet-moped-entlassungsart-valueset.xlsx
+++ b/r5-ELGA-MOPED-354-operations-updaten-und-erheben/ValueSet-moped-entlassungsart-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T19:32:49+00:00</t>
+    <t>2025-02-13T20:08:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-354-operations-updaten-und-erheben/ValueSet-moped-entlassungsart-valueset.xlsx
+++ b/r5-ELGA-MOPED-354-operations-updaten-und-erheben/ValueSet-moped-entlassungsart-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T20:08:18+00:00</t>
+    <t>2025-02-14T09:18:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
